--- a/pdfs/excel/2024-2025.xlsx
+++ b/pdfs/excel/2024-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS_PC\OneDrive\Desktop\MG\Group_3_mini_project\pdfs\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3693B61-9AFC-4CFB-A6FA-DCA98D5C7E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094A8FB8-2810-4DDE-B005-38ECAA5B8C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -179,16 +179,6 @@
         <family val="1"/>
       </rPr>
       <t>Battambang</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Kampong Cham 10</t>
     </r>
   </si>
   <si>
@@ -2172,6 +2162,9 @@
   <si>
     <t>Senior high school Classes</t>
   </si>
+  <si>
+    <t>Kampong Cham</t>
+  </si>
 </sst>
 </file>
 
@@ -2415,23 +2408,17 @@
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2452,13 +2439,22 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="8"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="8"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2469,13 +2465,40 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2535,29 +2558,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2579,6 +2599,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
@@ -2611,55 +2643,16 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3016,44 +3009,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30" t="s">
+      <c r="F1" s="35"/>
+      <c r="G1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="31"/>
-      <c r="I1" s="32" t="s">
+      <c r="H1" s="29"/>
+      <c r="I1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="33"/>
-      <c r="K1" s="34" t="s">
+      <c r="J1" s="31"/>
+      <c r="K1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="28" t="s">
+      <c r="L1" s="33"/>
+      <c r="M1" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="29"/>
+      <c r="N1" s="35"/>
     </row>
     <row r="2" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
       <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
@@ -3175,7 +3168,7 @@
     </row>
     <row r="5" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>14</v>
+        <v>218</v>
       </c>
       <c r="B5" s="7">
         <v>831</v>
@@ -3219,7 +3212,7 @@
     </row>
     <row r="6" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="7">
         <v>480</v>
@@ -3263,7 +3256,7 @@
     </row>
     <row r="7" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7">
         <v>644</v>
@@ -3307,7 +3300,7 @@
     </row>
     <row r="8" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="7">
         <v>805</v>
@@ -3351,7 +3344,7 @@
     </row>
     <row r="9" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="7">
         <v>615</v>
@@ -3395,7 +3388,7 @@
     </row>
     <row r="10" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="7">
         <v>768</v>
@@ -3439,7 +3432,7 @@
     </row>
     <row r="11" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>50</v>
@@ -3483,7 +3476,7 @@
     </row>
     <row r="12" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7">
         <v>231</v>
@@ -3527,7 +3520,7 @@
     </row>
     <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="7">
         <v>453</v>
@@ -3571,7 +3564,7 @@
     </row>
     <row r="14" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7">
         <v>141</v>
@@ -3615,7 +3608,7 @@
     </row>
     <row r="15" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="7">
         <v>375</v>
@@ -3659,7 +3652,7 @@
     </row>
     <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7">
         <v>88</v>
@@ -3703,7 +3696,7 @@
     </row>
     <row r="17" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="7">
         <v>384</v>
@@ -3747,7 +3740,7 @@
     </row>
     <row r="18" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="7">
         <v>160</v>
@@ -3791,7 +3784,7 @@
     </row>
     <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="7">
         <v>415</v>
@@ -3835,7 +3828,7 @@
     </row>
     <row r="20" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8">
         <v>1100</v>
@@ -3879,7 +3872,7 @@
     </row>
     <row r="21" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="7">
         <v>558</v>
@@ -3923,7 +3916,7 @@
     </row>
     <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="7">
         <v>343</v>
@@ -3967,7 +3960,7 @@
     </row>
     <row r="23" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8">
         <v>1165</v>
@@ -4011,7 +4004,7 @@
     </row>
     <row r="24" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7">
         <v>268</v>
@@ -4055,7 +4048,7 @@
     </row>
     <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="7">
         <v>518</v>
@@ -4099,7 +4092,7 @@
     </row>
     <row r="26" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="7">
         <v>811</v>
@@ -4143,7 +4136,7 @@
     </row>
     <row r="27" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="7">
         <v>747</v>
@@ -4187,7 +4180,7 @@
     </row>
     <row r="28" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>13948</v>
@@ -4231,7 +4224,7 @@
     </row>
     <row r="29" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="8">
         <v>1579</v>
@@ -4275,7 +4268,7 @@
     </row>
     <row r="30" spans="1:14" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>12369</v>
@@ -4354,75 +4347,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="31"/>
+      <c r="D1" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="45" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="46"/>
-      <c r="F1" s="32" t="s">
+      <c r="G1" s="31"/>
+      <c r="H1" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="32" t="s">
+      <c r="I1" s="31"/>
+      <c r="J1" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="I1" s="33"/>
-      <c r="J1" s="32" t="s">
+      <c r="K1" s="31"/>
+      <c r="L1" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="52" t="s">
+      <c r="M1" s="63"/>
+      <c r="N1" s="64"/>
+    </row>
+    <row r="2" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="37"/>
+      <c r="B2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="M1" s="53"/>
-      <c r="N1" s="54"/>
-    </row>
-    <row r="2" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L2" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -4515,7 +4508,7 @@
     </row>
     <row r="5" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8">
         <v>1645</v>
@@ -4559,7 +4552,7 @@
     </row>
     <row r="6" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="7">
         <v>938</v>
@@ -4603,7 +4596,7 @@
     </row>
     <row r="7" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>1143</v>
@@ -4647,7 +4640,7 @@
     </row>
     <row r="8" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8">
         <v>1404</v>
@@ -4691,7 +4684,7 @@
     </row>
     <row r="9" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8">
         <v>1174</v>
@@ -4735,7 +4728,7 @@
     </row>
     <row r="10" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8">
         <v>1704</v>
@@ -4779,7 +4772,7 @@
     </row>
     <row r="11" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>93</v>
@@ -4823,7 +4816,7 @@
     </row>
     <row r="12" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7">
         <v>299</v>
@@ -4867,7 +4860,7 @@
     </row>
     <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="7">
         <v>772</v>
@@ -4911,7 +4904,7 @@
     </row>
     <row r="14" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7">
         <v>282</v>
@@ -4955,7 +4948,7 @@
     </row>
     <row r="15" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="7">
         <v>529</v>
@@ -4999,7 +4992,7 @@
     </row>
     <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7">
         <v>158</v>
@@ -5043,7 +5036,7 @@
     </row>
     <row r="17" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="8">
         <v>1091</v>
@@ -5087,7 +5080,7 @@
     </row>
     <row r="18" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="7">
         <v>280</v>
@@ -5131,7 +5124,7 @@
     </row>
     <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="7">
         <v>647</v>
@@ -5175,7 +5168,7 @@
     </row>
     <row r="20" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8">
         <v>2080</v>
@@ -5219,7 +5212,7 @@
     </row>
     <row r="21" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="7">
         <v>875</v>
@@ -5263,7 +5256,7 @@
     </row>
     <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="7">
         <v>586</v>
@@ -5307,7 +5300,7 @@
     </row>
     <row r="23" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8">
         <v>2156</v>
@@ -5351,7 +5344,7 @@
     </row>
     <row r="24" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7">
         <v>429</v>
@@ -5395,7 +5388,7 @@
     </row>
     <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="8">
         <v>1130</v>
@@ -5439,7 +5432,7 @@
     </row>
     <row r="26" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8">
         <v>1943</v>
@@ -5483,7 +5476,7 @@
     </row>
     <row r="27" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="8">
         <v>1147</v>
@@ -5527,7 +5520,7 @@
     </row>
     <row r="28" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>25921</v>
@@ -5571,7 +5564,7 @@
     </row>
     <row r="29" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="8">
         <v>3865</v>
@@ -5615,7 +5608,7 @@
     </row>
     <row r="30" spans="1:14" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>22056</v>
@@ -5687,53 +5680,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="68"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" s="58"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="60" t="s">
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="61"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="52" t="s">
+      <c r="J1" s="64"/>
+    </row>
+    <row r="2" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="37"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="J1" s="54"/>
-    </row>
-    <row r="2" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -5802,7 +5795,7 @@
     </row>
     <row r="5" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8">
         <v>5023</v>
@@ -5834,7 +5827,7 @@
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="8">
         <v>2652</v>
@@ -5866,7 +5859,7 @@
     </row>
     <row r="7" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>3474</v>
@@ -5898,7 +5891,7 @@
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8">
         <v>3876</v>
@@ -5930,7 +5923,7 @@
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8">
         <v>3317</v>
@@ -5962,7 +5955,7 @@
     </row>
     <row r="10" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8">
         <v>5762</v>
@@ -5994,7 +5987,7 @@
     </row>
     <row r="11" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>259</v>
@@ -6026,7 +6019,7 @@
     </row>
     <row r="12" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7">
         <v>879</v>
@@ -6058,7 +6051,7 @@
     </row>
     <row r="13" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="8">
         <v>2215</v>
@@ -6090,7 +6083,7 @@
     </row>
     <row r="14" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7">
         <v>735</v>
@@ -6122,7 +6115,7 @@
     </row>
     <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8">
         <v>1644</v>
@@ -6154,7 +6147,7 @@
     </row>
     <row r="16" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7">
         <v>459</v>
@@ -6186,7 +6179,7 @@
     </row>
     <row r="17" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="8">
         <v>4050</v>
@@ -6218,7 +6211,7 @@
     </row>
     <row r="18" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="8">
         <v>1116</v>
@@ -6250,7 +6243,7 @@
     </row>
     <row r="19" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="8">
         <v>1919</v>
@@ -6282,7 +6275,7 @@
     </row>
     <row r="20" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8">
         <v>6017</v>
@@ -6314,7 +6307,7 @@
     </row>
     <row r="21" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="8">
         <v>2714</v>
@@ -6346,7 +6339,7 @@
     </row>
     <row r="22" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="8">
         <v>1474</v>
@@ -6378,7 +6371,7 @@
     </row>
     <row r="23" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8">
         <v>5954</v>
@@ -6410,7 +6403,7 @@
     </row>
     <row r="24" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="8">
         <v>1191</v>
@@ -6442,7 +6435,7 @@
     </row>
     <row r="25" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="8">
         <v>3121</v>
@@ -6474,7 +6467,7 @@
     </row>
     <row r="26" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8">
         <v>5292</v>
@@ -6506,7 +6499,7 @@
     </row>
     <row r="27" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="8">
         <v>3937</v>
@@ -6538,7 +6531,7 @@
     </row>
     <row r="28" spans="1:10" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>77150</v>
@@ -6570,7 +6563,7 @@
     </row>
     <row r="29" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="8">
         <v>13377</v>
@@ -6602,7 +6595,7 @@
     </row>
     <row r="30" spans="1:10" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>63773</v>
@@ -6661,63 +6654,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="31"/>
+      <c r="D1" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="26" t="s">
+      <c r="E1" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="F1" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="29"/>
+    </row>
+    <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="37"/>
+      <c r="B2" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="31"/>
-    </row>
-    <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="J2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="M2" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -6804,7 +6797,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8">
         <v>9579</v>
@@ -6845,7 +6838,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="8">
         <v>27827</v>
@@ -6886,7 +6879,7 @@
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>15710</v>
@@ -6927,7 +6920,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8">
         <v>13998</v>
@@ -6968,7 +6961,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8">
         <v>16455</v>
@@ -7009,7 +7002,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8">
         <v>22419</v>
@@ -7050,7 +7043,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="8">
         <v>13175</v>
@@ -7091,7 +7084,7 @@
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="8">
         <v>13539</v>
@@ -7132,7 +7125,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="8">
         <v>83325</v>
@@ -7173,7 +7166,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="8">
         <v>20796</v>
@@ -7214,7 +7207,7 @@
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8">
         <v>20339</v>
@@ -7255,7 +7248,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="8">
         <v>15479</v>
@@ -7296,7 +7289,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="8">
         <v>10492</v>
@@ -7337,7 +7330,7 @@
     </row>
     <row r="18" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="8">
         <v>25254</v>
@@ -7378,7 +7371,7 @@
     </row>
     <row r="19" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="8">
         <v>1581355</v>
@@ -7419,7 +7412,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8">
         <v>28674</v>
@@ -7460,7 +7453,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="8">
         <v>28348</v>
@@ -7501,7 +7494,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="8">
         <v>14349</v>
@@ -7542,7 +7535,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8">
         <v>15192</v>
@@ -7583,7 +7576,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="8">
         <v>17455</v>
@@ -7624,7 +7617,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="8">
         <v>44298</v>
@@ -7665,7 +7658,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8">
         <v>73755</v>
@@ -7706,7 +7699,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="8">
         <v>15271</v>
@@ -7747,7 +7740,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>75164</v>
@@ -7788,7 +7781,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="8">
         <v>22171</v>
@@ -7829,7 +7822,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>82164</v>
@@ -7901,40 +7894,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="26" t="s">
+      <c r="G1" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="H1" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="I1" s="35"/>
+      <c r="J1" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="I1" s="29"/>
-      <c r="J1" s="57" t="s">
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="69"/>
+    </row>
+    <row r="2" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="37"/>
+      <c r="B2" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="59"/>
-    </row>
-    <row r="2" spans="1:14" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>144</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>9</v>
@@ -7942,28 +7935,28 @@
       <c r="E2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
       <c r="H2" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L2" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="N2" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -8056,7 +8049,7 @@
     </row>
     <row r="5" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="7">
         <v>690</v>
@@ -8100,7 +8093,7 @@
     </row>
     <row r="6" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="7">
         <v>441</v>
@@ -8144,7 +8137,7 @@
     </row>
     <row r="7" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7">
         <v>587</v>
@@ -8188,7 +8181,7 @@
     </row>
     <row r="8" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="7">
         <v>757</v>
@@ -8232,7 +8225,7 @@
     </row>
     <row r="9" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="7">
         <v>573</v>
@@ -8276,7 +8269,7 @@
     </row>
     <row r="10" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="7">
         <v>702</v>
@@ -8320,7 +8313,7 @@
     </row>
     <row r="11" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>39</v>
@@ -8364,7 +8357,7 @@
     </row>
     <row r="12" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7">
         <v>217</v>
@@ -8408,7 +8401,7 @@
     </row>
     <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="7">
         <v>422</v>
@@ -8452,7 +8445,7 @@
     </row>
     <row r="14" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7">
         <v>123</v>
@@ -8496,7 +8489,7 @@
     </row>
     <row r="15" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="7">
         <v>359</v>
@@ -8540,7 +8533,7 @@
     </row>
     <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7">
         <v>77</v>
@@ -8584,7 +8577,7 @@
     </row>
     <row r="17" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="7">
         <v>362</v>
@@ -8628,7 +8621,7 @@
     </row>
     <row r="18" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="7">
         <v>149</v>
@@ -8672,7 +8665,7 @@
     </row>
     <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="7">
         <v>360</v>
@@ -8716,7 +8709,7 @@
     </row>
     <row r="20" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="7">
         <v>970</v>
@@ -8760,7 +8753,7 @@
     </row>
     <row r="21" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="7">
         <v>471</v>
@@ -8804,7 +8797,7 @@
     </row>
     <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="7">
         <v>327</v>
@@ -8848,7 +8841,7 @@
     </row>
     <row r="23" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="7">
         <v>954</v>
@@ -8892,7 +8885,7 @@
     </row>
     <row r="24" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7">
         <v>253</v>
@@ -8936,7 +8929,7 @@
     </row>
     <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="7">
         <v>438</v>
@@ -8980,7 +8973,7 @@
     </row>
     <row r="26" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="7">
         <v>720</v>
@@ -9024,7 +9017,7 @@
     </row>
     <row r="27" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="7">
         <v>694</v>
@@ -9068,7 +9061,7 @@
     </row>
     <row r="28" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>12494</v>
@@ -9112,7 +9105,7 @@
     </row>
     <row r="29" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="8">
         <v>1429</v>
@@ -9156,7 +9149,7 @@
     </row>
     <row r="30" spans="1:14" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>11065</v>
@@ -9229,34 +9222,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="30" t="s">
+      <c r="B1" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="29"/>
+      <c r="D1" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="28" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="28" t="s">
+      <c r="I1" s="35"/>
+      <c r="J1" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="I1" s="29"/>
-      <c r="J1" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="31"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="29"/>
     </row>
     <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
@@ -9282,16 +9275,16 @@
         <v>10</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -9378,7 +9371,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8">
         <v>17634</v>
@@ -9419,7 +9412,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="8">
         <v>11236</v>
@@ -9460,7 +9453,7 @@
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>17242</v>
@@ -9501,7 +9494,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8">
         <v>15390</v>
@@ -9542,7 +9535,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8">
         <v>11678</v>
@@ -9583,7 +9576,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8">
         <v>23003</v>
@@ -9624,7 +9617,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>889</v>
@@ -9665,7 +9658,7 @@
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="8">
         <v>2425</v>
@@ -9706,7 +9699,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="8">
         <v>8811</v>
@@ -9747,7 +9740,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="8">
         <v>2289</v>
@@ -9788,7 +9781,7 @@
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8">
         <v>6391</v>
@@ -9829,7 +9822,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="8">
         <v>1639</v>
@@ -9870,7 +9863,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="8">
         <v>35924</v>
@@ -9911,7 +9904,7 @@
     </row>
     <row r="18" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="8">
         <v>4888</v>
@@ -9952,7 +9945,7 @@
     </row>
     <row r="19" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="8">
         <v>6389</v>
@@ -9993,7 +9986,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8">
         <v>22937</v>
@@ -10034,7 +10027,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="8">
         <v>9733</v>
@@ -10075,7 +10068,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="8">
         <v>4831</v>
@@ -10116,7 +10109,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8">
         <v>22483</v>
@@ -10157,7 +10150,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="8">
         <v>4185</v>
@@ -10198,7 +10191,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="8">
         <v>11212</v>
@@ -10239,7 +10232,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8">
         <v>17129</v>
@@ -10280,7 +10273,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="8">
         <v>16327</v>
@@ -10321,7 +10314,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>312199</v>
@@ -10362,7 +10355,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B29" s="8">
         <v>77593</v>
@@ -10403,7 +10396,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B30" s="8">
         <v>234606</v>
@@ -10470,57 +10463,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="79" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="C1" s="74" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="D1" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="E1" s="74" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="F1" s="74" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="G1" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="H1" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="I1" s="76" t="s">
         <v>165</v>
       </c>
-      <c r="I1" s="42" t="s">
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="78"/>
+    </row>
+    <row r="2" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="80"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="44"/>
-    </row>
-    <row r="2" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="65"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="K2" s="12" t="s">
+      <c r="L2" s="12" t="s">
         <v>168</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -10601,7 +10594,7 @@
     </row>
     <row r="5" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="13">
         <v>276.7</v>
@@ -10639,7 +10632,7 @@
     </row>
     <row r="6" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="13">
         <v>262.2</v>
@@ -10677,7 +10670,7 @@
     </row>
     <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="13">
         <v>281.7</v>
@@ -10715,7 +10708,7 @@
     </row>
     <row r="8" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="13">
         <v>206.2</v>
@@ -10753,7 +10746,7 @@
     </row>
     <row r="9" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="13">
         <v>216.5</v>
@@ -10791,7 +10784,7 @@
     </row>
     <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="13">
         <v>371.6</v>
@@ -10829,7 +10822,7 @@
     </row>
     <row r="11" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="13">
         <v>194.2</v>
@@ -10867,7 +10860,7 @@
     </row>
     <row r="12" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="13">
         <v>132.6</v>
@@ -10905,7 +10898,7 @@
     </row>
     <row r="13" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="13">
         <v>208.2</v>
@@ -10943,7 +10936,7 @@
     </row>
     <row r="14" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="13">
         <v>180.4</v>
@@ -10981,7 +10974,7 @@
     </row>
     <row r="15" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="13">
         <v>157.1</v>
@@ -11019,7 +11012,7 @@
     </row>
     <row r="16" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="13">
         <v>204.8</v>
@@ -11057,7 +11050,7 @@
     </row>
     <row r="17" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="13">
         <v>679.9</v>
@@ -11095,7 +11088,7 @@
     </row>
     <row r="18" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="13">
         <v>335.1</v>
@@ -11133,7 +11126,7 @@
     </row>
     <row r="19" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="13">
         <v>154.30000000000001</v>
@@ -11171,7 +11164,7 @@
     </row>
     <row r="20" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="13">
         <v>227.9</v>
@@ -11209,7 +11202,7 @@
     </row>
     <row r="21" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="13">
         <v>208.1</v>
@@ -11247,7 +11240,7 @@
     </row>
     <row r="22" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="13">
         <v>169.1</v>
@@ -11285,7 +11278,7 @@
     </row>
     <row r="23" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="13">
         <v>254.1</v>
@@ -11323,7 +11316,7 @@
     </row>
     <row r="24" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="13">
         <v>157.6</v>
@@ -11361,7 +11354,7 @@
     </row>
     <row r="25" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="13">
         <v>249.8</v>
@@ -11399,7 +11392,7 @@
     </row>
     <row r="26" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="13">
         <v>255.1</v>
@@ -11437,7 +11430,7 @@
     </row>
     <row r="27" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="13">
         <v>234.1</v>
@@ -11475,7 +11468,7 @@
     </row>
     <row r="28" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="15">
         <v>246.4</v>
@@ -11513,7 +11506,7 @@
     </row>
     <row r="29" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="13">
         <v>442.9</v>
@@ -11551,7 +11544,7 @@
     </row>
     <row r="30" spans="1:12" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="13">
         <v>221.2</v>
@@ -11623,63 +11616,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="68" t="s">
-        <v>158</v>
-      </c>
-      <c r="B1" s="70" t="s">
+      <c r="A1" s="88" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="90" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="74" t="s">
         <v>170</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="D1" s="74" t="s">
         <v>171</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="E1" s="81" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="72" t="s">
+      <c r="F1" s="74" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="G1" s="81" t="s">
         <v>174</v>
       </c>
-      <c r="G1" s="72" t="s">
+      <c r="H1" s="83" t="s">
         <v>175</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="86" t="s">
         <v>176</v>
       </c>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="77" t="s">
+      <c r="M1" s="87"/>
+    </row>
+    <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="89"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L2" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="M1" s="78"/>
-    </row>
-    <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="69"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="12" t="s">
         <v>178</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -11766,7 +11759,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="13">
         <v>38.4</v>
@@ -11807,7 +11800,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="13">
         <v>35.799999999999997</v>
@@ -11848,7 +11841,7 @@
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="13">
         <v>41.6</v>
@@ -11889,7 +11882,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="13">
         <v>37.299999999999997</v>
@@ -11930,7 +11923,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="13">
         <v>27.8</v>
@@ -11971,7 +11964,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="13">
         <v>38.9</v>
@@ -12012,7 +12005,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="13">
         <v>21.1</v>
@@ -12053,7 +12046,7 @@
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="13">
         <v>24.8</v>
@@ -12094,7 +12087,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="13">
         <v>34.299999999999997</v>
@@ -12135,7 +12128,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="13">
         <v>26.5</v>
@@ -12176,7 +12169,7 @@
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="13">
         <v>35.200000000000003</v>
@@ -12217,7 +12210,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="13">
         <v>27.5</v>
@@ -12258,7 +12251,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="13">
         <v>29.4</v>
@@ -12299,7 +12292,7 @@
     </row>
     <row r="18" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="13">
         <v>32.700000000000003</v>
@@ -12340,7 +12333,7 @@
     </row>
     <row r="19" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="13">
         <v>29.1</v>
@@ -12381,7 +12374,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="13">
         <v>42.1</v>
@@ -12422,7 +12415,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="13">
         <v>37.9</v>
@@ -12463,7 +12456,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="13">
         <v>38.299999999999997</v>
@@ -12504,7 +12497,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="13">
         <v>44.4</v>
@@ -12545,7 +12538,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="13">
         <v>29.5</v>
@@ -12586,7 +12579,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="13">
         <v>35.6</v>
@@ -12627,7 +12620,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="13">
         <v>32.6</v>
@@ -12668,7 +12661,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="13">
         <v>44</v>
@@ -12709,7 +12702,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="15">
         <v>36</v>
@@ -12750,7 +12743,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="13">
         <v>30.1</v>
@@ -12791,7 +12784,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="13">
         <v>38</v>
@@ -12858,67 +12851,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="92" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="93"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="95" t="s">
         <v>180</v>
       </c>
-      <c r="C1" s="80"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="82" t="s">
+      <c r="F1" s="96"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="98" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="85" t="s">
+      <c r="I1" s="99"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I1" s="86"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="L1" s="88"/>
-      <c r="M1" s="29"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="35"/>
     </row>
     <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="H2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="K2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -13005,7 +12998,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="13">
         <v>6.9</v>
@@ -13046,7 +13039,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="13">
         <v>5.0999999999999996</v>
@@ -13087,7 +13080,7 @@
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="13">
         <v>4.5999999999999996</v>
@@ -13128,7 +13121,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="13">
         <v>6</v>
@@ -13169,7 +13162,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="13">
         <v>3.8</v>
@@ -13210,7 +13203,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="13">
         <v>7.4</v>
@@ -13251,7 +13244,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="13">
         <v>3.8</v>
@@ -13292,7 +13285,7 @@
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="13">
         <v>4</v>
@@ -13333,7 +13326,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="13">
         <v>6.4</v>
@@ -13374,7 +13367,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="13">
         <v>5.3</v>
@@ -13415,7 +13408,7 @@
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="13">
         <v>5.7</v>
@@ -13456,7 +13449,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="13">
         <v>3</v>
@@ -13497,7 +13490,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="13">
         <v>3.2</v>
@@ -13538,7 +13531,7 @@
     </row>
     <row r="18" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="13">
         <v>2.6</v>
@@ -13579,7 +13572,7 @@
     </row>
     <row r="19" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="13">
         <v>8.1</v>
@@ -13620,7 +13613,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="13">
         <v>5.8</v>
@@ -13661,7 +13654,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="13">
         <v>6</v>
@@ -13702,7 +13695,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="13">
         <v>5</v>
@@ -13743,7 +13736,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="13">
         <v>6.5</v>
@@ -13784,7 +13777,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="13">
         <v>8.5</v>
@@ -13825,7 +13818,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="13">
         <v>3.6</v>
@@ -13866,7 +13859,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="13">
         <v>4.8</v>
@@ -13907,7 +13900,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="13">
         <v>6.6</v>
@@ -13948,7 +13941,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="15">
         <v>5.5</v>
@@ -13989,7 +13982,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B29" s="13">
         <v>3.9</v>
@@ -14030,7 +14023,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B30" s="13">
         <v>5.8</v>
@@ -14095,32 +14088,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="95" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="97"/>
+      <c r="D1" s="95" t="s">
         <v>184</v>
       </c>
-      <c r="C1" s="84"/>
-      <c r="D1" s="82" t="s">
+      <c r="E1" s="97"/>
+      <c r="F1" s="104" t="s">
         <v>185</v>
       </c>
-      <c r="E1" s="84"/>
-      <c r="F1" s="89" t="s">
+      <c r="G1" s="105"/>
+      <c r="H1" s="102" t="s">
         <v>186</v>
       </c>
-      <c r="G1" s="90"/>
-      <c r="H1" s="91" t="s">
+      <c r="I1" s="103"/>
+      <c r="J1" s="102" t="s">
         <v>187</v>
       </c>
-      <c r="I1" s="92"/>
-      <c r="J1" s="91" t="s">
-        <v>188</v>
-      </c>
-      <c r="K1" s="92"/>
+      <c r="K1" s="103"/>
     </row>
     <row r="2" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -14224,7 +14217,7 @@
     </row>
     <row r="5" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="13">
         <v>121.4</v>
@@ -14259,7 +14252,7 @@
     </row>
     <row r="6" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="13">
         <v>106.8</v>
@@ -14294,7 +14287,7 @@
     </row>
     <row r="7" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="13">
         <v>105</v>
@@ -14329,7 +14322,7 @@
     </row>
     <row r="8" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="13">
         <v>114.3</v>
@@ -14364,7 +14357,7 @@
     </row>
     <row r="9" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="13">
         <v>112.4</v>
@@ -14399,7 +14392,7 @@
     </row>
     <row r="10" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="13">
         <v>116.6</v>
@@ -14434,7 +14427,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="13">
         <v>102.6</v>
@@ -14469,7 +14462,7 @@
     </row>
     <row r="12" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="13">
         <v>128.4</v>
@@ -14504,7 +14497,7 @@
     </row>
     <row r="13" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="13">
         <v>122.9</v>
@@ -14539,7 +14532,7 @@
     </row>
     <row r="14" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="13">
         <v>123.3</v>
@@ -14574,7 +14567,7 @@
     </row>
     <row r="15" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="23">
         <v>95.9</v>
@@ -14609,7 +14602,7 @@
     </row>
     <row r="16" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="13">
         <v>104</v>
@@ -14644,7 +14637,7 @@
     </row>
     <row r="17" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="23">
         <v>62.1</v>
@@ -14679,7 +14672,7 @@
     </row>
     <row r="18" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="13">
         <v>111.3</v>
@@ -14714,7 +14707,7 @@
     </row>
     <row r="19" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="13">
         <v>107.9</v>
@@ -14749,7 +14742,7 @@
     </row>
     <row r="20" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="23">
         <v>96.1</v>
@@ -14784,7 +14777,7 @@
     </row>
     <row r="21" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="13">
         <v>116.1</v>
@@ -14819,7 +14812,7 @@
     </row>
     <row r="22" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="13">
         <v>135.1</v>
@@ -14854,7 +14847,7 @@
     </row>
     <row r="23" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="13">
         <v>113.6</v>
@@ -14889,7 +14882,7 @@
     </row>
     <row r="24" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="13">
         <v>110.4</v>
@@ -14924,7 +14917,7 @@
     </row>
     <row r="25" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="13">
         <v>102</v>
@@ -14959,7 +14952,7 @@
     </row>
     <row r="26" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="13">
         <v>106.5</v>
@@ -14994,7 +14987,7 @@
     </row>
     <row r="27" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="13">
         <v>104</v>
@@ -15029,7 +15022,7 @@
     </row>
     <row r="28" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="15">
         <v>104.8</v>
@@ -15064,7 +15057,7 @@
     </row>
     <row r="29" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B29" s="23">
         <v>76.400000000000006</v>
@@ -15099,7 +15092,7 @@
     </row>
     <row r="30" spans="1:11" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B30" s="13">
         <v>114.2</v>
@@ -15157,67 +15150,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="73"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="30" t="s">
+      <c r="F1" s="73"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="30" t="s">
+      <c r="I1" s="73"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="I1" s="63"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="30" t="s">
+      <c r="L1" s="73"/>
+      <c r="M1" s="29"/>
+    </row>
+    <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="37"/>
+      <c r="B2" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="L1" s="63"/>
-      <c r="M1" s="31"/>
-    </row>
-    <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="E2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="H2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="K2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -15304,7 +15297,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="13">
         <v>86.5</v>
@@ -15345,7 +15338,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="13">
         <v>90.8</v>
@@ -15386,7 +15379,7 @@
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="13">
         <v>91.9</v>
@@ -15427,7 +15420,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="13">
         <v>84.5</v>
@@ -15468,7 +15461,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="13">
         <v>90.2</v>
@@ -15509,7 +15502,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="13">
         <v>87</v>
@@ -15550,7 +15543,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="13">
         <v>94.2</v>
@@ -15591,7 +15584,7 @@
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="13">
         <v>91</v>
@@ -15632,7 +15625,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="13">
         <v>84.1</v>
@@ -15673,7 +15666,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="13">
         <v>91.5</v>
@@ -15714,7 +15707,7 @@
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="13">
         <v>86.9</v>
@@ -15755,7 +15748,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="13">
         <v>85.6</v>
@@ -15796,7 +15789,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="13">
         <v>93.7</v>
@@ -15837,7 +15830,7 @@
     </row>
     <row r="18" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="13">
         <v>91.6</v>
@@ -15878,7 +15871,7 @@
     </row>
     <row r="19" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="13">
         <v>80</v>
@@ -15919,7 +15912,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="13">
         <v>89</v>
@@ -15960,7 +15953,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="13">
         <v>86</v>
@@ -16001,7 +15994,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="13">
         <v>83.8</v>
@@ -16042,7 +16035,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="13">
         <v>86.6</v>
@@ -16083,7 +16076,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="13">
         <v>80.3</v>
@@ -16124,7 +16117,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="13">
         <v>92.8</v>
@@ -16165,7 +16158,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="13">
         <v>91.2</v>
@@ -16206,7 +16199,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="13">
         <v>84.5</v>
@@ -16247,7 +16240,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="15">
         <v>88.1</v>
@@ -16288,7 +16281,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B29" s="13">
         <v>91</v>
@@ -16329,7 +16322,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B30" s="13">
         <v>87.4</v>
@@ -16398,70 +16391,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="26" t="s">
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="H1" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="I1" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="J1" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="K1" s="33"/>
+      <c r="L1" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="32" t="s">
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="31"/>
+    </row>
+    <row r="2" spans="1:15" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="37"/>
+      <c r="B2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="33"/>
-    </row>
-    <row r="2" spans="1:15" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="M2" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>54</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>11</v>
@@ -16563,7 +16556,7 @@
     </row>
     <row r="5" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="7">
         <v>297</v>
@@ -16610,7 +16603,7 @@
     </row>
     <row r="6" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="7">
         <v>121</v>
@@ -16657,7 +16650,7 @@
     </row>
     <row r="7" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7">
         <v>231</v>
@@ -16704,7 +16697,7 @@
     </row>
     <row r="8" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="7">
         <v>216</v>
@@ -16751,7 +16744,7 @@
     </row>
     <row r="9" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="7">
         <v>203</v>
@@ -16798,7 +16791,7 @@
     </row>
     <row r="10" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="7">
         <v>253</v>
@@ -16845,7 +16838,7 @@
     </row>
     <row r="11" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>22</v>
@@ -16892,7 +16885,7 @@
     </row>
     <row r="12" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7">
         <v>77</v>
@@ -16939,7 +16932,7 @@
     </row>
     <row r="13" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="7">
         <v>112</v>
@@ -16986,7 +16979,7 @@
     </row>
     <row r="14" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7">
         <v>35</v>
@@ -17033,7 +17026,7 @@
     </row>
     <row r="15" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="7">
         <v>115</v>
@@ -17080,7 +17073,7 @@
     </row>
     <row r="16" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7">
         <v>26</v>
@@ -17127,7 +17120,7 @@
     </row>
     <row r="17" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="7">
         <v>152</v>
@@ -17174,7 +17167,7 @@
     </row>
     <row r="18" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="7">
         <v>59</v>
@@ -17221,7 +17214,7 @@
     </row>
     <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="7">
         <v>120</v>
@@ -17268,7 +17261,7 @@
     </row>
     <row r="20" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="7">
         <v>424</v>
@@ -17315,7 +17308,7 @@
     </row>
     <row r="21" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="7">
         <v>189</v>
@@ -17362,7 +17355,7 @@
     </row>
     <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="7">
         <v>75</v>
@@ -17409,7 +17402,7 @@
     </row>
     <row r="23" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="7">
         <v>468</v>
@@ -17456,7 +17449,7 @@
     </row>
     <row r="24" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7">
         <v>51</v>
@@ -17503,7 +17496,7 @@
     </row>
     <row r="25" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="7">
         <v>182</v>
@@ -17550,7 +17543,7 @@
     </row>
     <row r="26" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="7">
         <v>309</v>
@@ -17597,7 +17590,7 @@
     </row>
     <row r="27" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="7">
         <v>260</v>
@@ -17644,7 +17637,7 @@
     </row>
     <row r="28" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>4725</v>
@@ -17691,7 +17684,7 @@
     </row>
     <row r="29" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="7">
         <v>572</v>
@@ -17738,7 +17731,7 @@
     </row>
     <row r="30" spans="1:15" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>4153</v>
@@ -17810,67 +17803,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1" s="73"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="30" t="s">
+      <c r="F1" s="73"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="30" t="s">
+      <c r="I1" s="73"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="I1" s="63"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="L1" s="63"/>
-      <c r="M1" s="31"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="29"/>
     </row>
     <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="E2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="H2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="K2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -17957,7 +17950,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="13">
         <v>89.3</v>
@@ -17998,7 +17991,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="13">
         <v>93.3</v>
@@ -18039,7 +18032,7 @@
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="13">
         <v>92.5</v>
@@ -18080,7 +18073,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="13">
         <v>91</v>
@@ -18121,7 +18114,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="13">
         <v>93.1</v>
@@ -18162,7 +18155,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="13">
         <v>90.6</v>
@@ -18203,7 +18196,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="13">
         <v>92.8</v>
@@ -18244,7 +18237,7 @@
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="13">
         <v>94</v>
@@ -18285,7 +18278,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="13">
         <v>89</v>
@@ -18326,7 +18319,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="13">
         <v>90.5</v>
@@ -18367,7 +18360,7 @@
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="13">
         <v>90</v>
@@ -18408,7 +18401,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="13">
         <v>95.2</v>
@@ -18449,7 +18442,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="13">
         <v>97.6</v>
@@ -18490,7 +18483,7 @@
     </row>
     <row r="18" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="13">
         <v>97.6</v>
@@ -18531,7 +18524,7 @@
     </row>
     <row r="19" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="13">
         <v>87.5</v>
@@ -18572,7 +18565,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="13">
         <v>91.8</v>
@@ -18613,7 +18606,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="13">
         <v>89.9</v>
@@ -18654,7 +18647,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="13">
         <v>87.7</v>
@@ -18695,7 +18688,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="13">
         <v>92.4</v>
@@ -18736,7 +18729,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="13">
         <v>87.4</v>
@@ -18777,7 +18770,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="13">
         <v>94.9</v>
@@ -18818,7 +18811,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="13">
         <v>94.6</v>
@@ -18859,7 +18852,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="13">
         <v>90</v>
@@ -18900,7 +18893,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="15">
         <v>92</v>
@@ -18941,7 +18934,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B29" s="13">
         <v>95.8</v>
@@ -18982,7 +18975,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B30" s="13">
         <v>91.1</v>
@@ -19045,67 +19038,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" s="73"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="30" t="s">
+      <c r="F1" s="73"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="30" t="s">
+      <c r="I1" s="73"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="I1" s="63"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="L1" s="63"/>
-      <c r="M1" s="31"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="29"/>
     </row>
     <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="E2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="H2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="K2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -19192,7 +19185,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="13">
         <v>69.8</v>
@@ -19233,7 +19226,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="13">
         <v>84.9</v>
@@ -19274,7 +19267,7 @@
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="13">
         <v>75.599999999999994</v>
@@ -19315,7 +19308,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="13">
         <v>79.599999999999994</v>
@@ -19356,7 +19349,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="13">
         <v>75.099999999999994</v>
@@ -19397,7 +19390,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="13">
         <v>86.4</v>
@@ -19438,7 +19431,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="13">
         <v>84.6</v>
@@ -19479,7 +19472,7 @@
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="13">
         <v>79</v>
@@ -19520,7 +19513,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="13">
         <v>82.9</v>
@@ -19561,7 +19554,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="13">
         <v>79.5</v>
@@ -19602,7 +19595,7 @@
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="13">
         <v>81.3</v>
@@ -19643,7 +19636,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="13">
         <v>85.7</v>
@@ -19684,7 +19677,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="13">
         <v>60.7</v>
@@ -19725,7 +19718,7 @@
     </row>
     <row r="18" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="13">
         <v>80.2</v>
@@ -19766,7 +19759,7 @@
     </row>
     <row r="19" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="13">
         <v>77.400000000000006</v>
@@ -19807,7 +19800,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="13">
         <v>72.900000000000006</v>
@@ -19848,7 +19841,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="13">
         <v>87.5</v>
@@ -19889,7 +19882,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="13">
         <v>58.6</v>
@@ -19930,7 +19923,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="13">
         <v>79.2</v>
@@ -19971,7 +19964,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="13">
         <v>71.7</v>
@@ -20012,7 +20005,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="13">
         <v>74.599999999999994</v>
@@ -20053,7 +20046,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="13">
         <v>79</v>
@@ -20094,7 +20087,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="13">
         <v>71.8</v>
@@ -20135,7 +20128,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="15">
         <v>76</v>
@@ -20176,7 +20169,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B29" s="13">
         <v>71.7</v>
@@ -20217,7 +20210,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B30" s="13">
         <v>77.3</v>
@@ -20285,63 +20278,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="48" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="94" t="s">
+      <c r="C1" s="48" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="94" t="s">
+      <c r="D1" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="D1" s="95" t="s">
+      <c r="E1" s="51"/>
+      <c r="F1" s="52" t="s">
         <v>207</v>
       </c>
-      <c r="E1" s="96"/>
-      <c r="F1" s="97" t="s">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="54"/>
+    </row>
+    <row r="2" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="47"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="99"/>
-    </row>
-    <row r="2" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="100"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="102" t="s">
+      <c r="E2" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="E2" s="103" t="s">
+      <c r="F2" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="F2" s="104" t="s">
+      <c r="G2" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="G2" s="105" t="s">
+      <c r="H2" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="H2" s="104" t="s">
+      <c r="I2" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="I2" s="105" t="s">
+      <c r="J2" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="104" t="s">
+      <c r="K2" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="K2" s="105" t="s">
+      <c r="L2" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="L2" s="104" t="s">
+      <c r="M2" s="27" t="s">
         <v>217</v>
-      </c>
-      <c r="M2" s="105" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -20428,7 +20421,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="7">
         <v>410</v>
@@ -20469,7 +20462,7 @@
     </row>
     <row r="6" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="7">
         <v>281</v>
@@ -20510,7 +20503,7 @@
     </row>
     <row r="7" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7">
         <v>316</v>
@@ -20551,7 +20544,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="7">
         <v>497</v>
@@ -20592,7 +20585,7 @@
     </row>
     <row r="9" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="7">
         <v>311</v>
@@ -20633,7 +20626,7 @@
     </row>
     <row r="10" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="7">
         <v>373</v>
@@ -20674,7 +20667,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>22</v>
@@ -20715,7 +20708,7 @@
     </row>
     <row r="12" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7">
         <v>122</v>
@@ -20756,7 +20749,7 @@
     </row>
     <row r="13" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="7">
         <v>286</v>
@@ -20797,7 +20790,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7">
         <v>91</v>
@@ -20838,7 +20831,7 @@
     </row>
     <row r="15" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="7">
         <v>221</v>
@@ -20879,7 +20872,7 @@
     </row>
     <row r="16" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7">
         <v>53</v>
@@ -20920,7 +20913,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="7">
         <v>165</v>
@@ -20961,7 +20954,7 @@
     </row>
     <row r="18" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="7">
         <v>71</v>
@@ -21002,7 +20995,7 @@
     </row>
     <row r="19" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="7">
         <v>230</v>
@@ -21043,7 +21036,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="7">
         <v>551</v>
@@ -21084,7 +21077,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="7">
         <v>308</v>
@@ -21125,7 +21118,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="7">
         <v>233</v>
@@ -21166,7 +21159,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="7">
         <v>572</v>
@@ -21207,7 +21200,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7">
         <v>175</v>
@@ -21248,7 +21241,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="7">
         <v>262</v>
@@ -21289,7 +21282,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="7">
         <v>382</v>
@@ -21330,7 +21323,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="7">
         <v>407</v>
@@ -21371,7 +21364,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>7398</v>
@@ -21412,7 +21405,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="7">
         <v>745</v>
@@ -21453,7 +21446,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>6653</v>
@@ -21516,36 +21509,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="32" t="s">
+      <c r="E1" s="31"/>
+      <c r="F1" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="32" t="s">
+      <c r="I1" s="31"/>
+      <c r="J1" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="33"/>
-      <c r="J1" s="34" t="s">
+      <c r="K1" s="33"/>
+      <c r="L1" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="M1" s="33"/>
+      <c r="M1" s="31"/>
     </row>
     <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -21667,7 +21660,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8">
         <v>24211</v>
@@ -21708,7 +21701,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="8">
         <v>13238</v>
@@ -21749,7 +21742,7 @@
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>19697</v>
@@ -21790,7 +21783,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8">
         <v>19997</v>
@@ -21831,7 +21824,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8">
         <v>14268</v>
@@ -21872,7 +21865,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8">
         <v>30733</v>
@@ -21913,7 +21906,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>970</v>
@@ -21954,7 +21947,7 @@
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="8">
         <v>3371</v>
@@ -21995,7 +21988,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="8">
         <v>12278</v>
@@ -22036,7 +22029,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="8">
         <v>3082</v>
@@ -22077,7 +22070,7 @@
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8">
         <v>6839</v>
@@ -22118,7 +22111,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="8">
         <v>1810</v>
@@ -22159,7 +22152,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="8">
         <v>23838</v>
@@ -22200,7 +22193,7 @@
     </row>
     <row r="18" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="8">
         <v>5750</v>
@@ -22241,7 +22234,7 @@
     </row>
     <row r="19" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="8">
         <v>8303</v>
@@ -22282,7 +22275,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8">
         <v>24521</v>
@@ -22323,7 +22316,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="8">
         <v>12804</v>
@@ -22364,7 +22357,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="8">
         <v>7100</v>
@@ -22405,7 +22398,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8">
         <v>29294</v>
@@ -22446,7 +22439,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="8">
         <v>5653</v>
@@ -22487,7 +22480,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="8">
         <v>12386</v>
@@ -22528,7 +22521,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8">
         <v>20074</v>
@@ -22569,7 +22562,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="8">
         <v>19240</v>
@@ -22610,7 +22603,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>364860</v>
@@ -22651,7 +22644,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="8">
         <v>64633</v>
@@ -22692,7 +22685,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>300227</v>
@@ -22757,36 +22750,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="32" t="s">
+      <c r="E1" s="31"/>
+      <c r="F1" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="32" t="s">
+      <c r="I1" s="31"/>
+      <c r="J1" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="33"/>
-      <c r="J1" s="34" t="s">
+      <c r="K1" s="33"/>
+      <c r="L1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="M1" s="33"/>
+      <c r="M1" s="31"/>
     </row>
     <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -22908,7 +22901,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8">
         <v>23059</v>
@@ -22949,7 +22942,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="8">
         <v>13269</v>
@@ -22990,7 +22983,7 @@
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>19319</v>
@@ -23031,7 +23024,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8">
         <v>18196</v>
@@ -23072,7 +23065,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8">
         <v>13862</v>
@@ -23113,7 +23106,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8">
         <v>29926</v>
@@ -23154,7 +23147,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="8">
         <v>1018</v>
@@ -23195,7 +23188,7 @@
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="8">
         <v>3011</v>
@@ -23236,7 +23229,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="8">
         <v>10878</v>
@@ -23277,7 +23270,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="8">
         <v>2774</v>
@@ -23318,7 +23311,7 @@
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8">
         <v>6720</v>
@@ -23359,7 +23352,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="8">
         <v>2005</v>
@@ -23400,7 +23393,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="8">
         <v>26451</v>
@@ -23441,7 +23434,7 @@
     </row>
     <row r="18" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="8">
         <v>6193</v>
@@ -23482,7 +23475,7 @@
     </row>
     <row r="19" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="8">
         <v>6941</v>
@@ -23523,7 +23516,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8">
         <v>25145</v>
@@ -23564,7 +23557,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="8">
         <v>12700</v>
@@ -23605,7 +23598,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="8">
         <v>6352</v>
@@ -23646,7 +23639,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8">
         <v>29084</v>
@@ -23687,7 +23680,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="8">
         <v>4785</v>
@@ -23728,7 +23721,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="8">
         <v>13419</v>
@@ -23769,7 +23762,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8">
         <v>20272</v>
@@ -23810,7 +23803,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="8">
         <v>18433</v>
@@ -23851,7 +23844,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>359071</v>
@@ -23892,7 +23885,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="8">
         <v>69467</v>
@@ -23933,7 +23926,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>289604</v>
@@ -23998,36 +23991,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="32" t="s">
+      <c r="E1" s="31"/>
+      <c r="F1" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="32" t="s">
+      <c r="I1" s="31"/>
+      <c r="J1" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="33"/>
-      <c r="J1" s="34" t="s">
+      <c r="K1" s="33"/>
+      <c r="L1" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="M1" s="33"/>
+      <c r="M1" s="31"/>
     </row>
     <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -24149,7 +24142,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8">
         <v>17462</v>
@@ -24190,7 +24183,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="8">
         <v>9728</v>
@@ -24231,7 +24224,7 @@
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>13883</v>
@@ -24272,7 +24265,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8">
         <v>12552</v>
@@ -24313,7 +24306,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8">
         <v>10332</v>
@@ -24354,7 +24347,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8">
         <v>21254</v>
@@ -24395,7 +24388,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>660</v>
@@ -24436,7 +24429,7 @@
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="8">
         <v>2185</v>
@@ -24477,7 +24470,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="8">
         <v>6486</v>
@@ -24518,7 +24511,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="8">
         <v>1865</v>
@@ -24559,7 +24552,7 @@
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8">
         <v>4194</v>
@@ -24600,7 +24593,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="8">
         <v>1447</v>
@@ -24641,7 +24634,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="8">
         <v>21108</v>
@@ -24682,7 +24675,7 @@
     </row>
     <row r="18" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="8">
         <v>3942</v>
@@ -24723,7 +24716,7 @@
     </row>
     <row r="19" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="8">
         <v>4227</v>
@@ -24764,7 +24757,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8">
         <v>18832</v>
@@ -24805,7 +24798,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="8">
         <v>8543</v>
@@ -24846,7 +24839,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="8">
         <v>4104</v>
@@ -24887,7 +24880,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8">
         <v>20602</v>
@@ -24928,7 +24921,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="8">
         <v>2864</v>
@@ -24969,7 +24962,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="8">
         <v>10114</v>
@@ -25010,7 +25003,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8">
         <v>16140</v>
@@ -25051,7 +25044,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="8">
         <v>13144</v>
@@ -25092,7 +25085,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>258083</v>
@@ -25133,7 +25126,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="8">
         <v>54476</v>
@@ -25174,7 +25167,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>203607</v>
@@ -25239,36 +25232,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="34" t="s">
+      <c r="E1" s="33"/>
+      <c r="F1" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="34" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="34" t="s">
+      <c r="I1" s="33"/>
+      <c r="J1" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="34" t="s">
+      <c r="K1" s="33"/>
+      <c r="L1" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="M1" s="35"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -25390,7 +25383,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8">
         <v>10876</v>
@@ -25431,7 +25424,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="8">
         <v>6016</v>
@@ -25472,7 +25465,7 @@
     </row>
     <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>7493</v>
@@ -25513,7 +25506,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8">
         <v>6317</v>
@@ -25554,7 +25547,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8">
         <v>6013</v>
@@ -25595,7 +25588,7 @@
     </row>
     <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8">
         <v>14593</v>
@@ -25636,7 +25629,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>368</v>
@@ -25677,7 +25670,7 @@
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="8">
         <v>1328</v>
@@ -25718,7 +25711,7 @@
     </row>
     <row r="13" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="8">
         <v>3019</v>
@@ -25759,7 +25752,7 @@
     </row>
     <row r="14" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7">
         <v>938</v>
@@ -25800,7 +25793,7 @@
     </row>
     <row r="15" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8">
         <v>2043</v>
@@ -25841,7 +25834,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7">
         <v>829</v>
@@ -25882,7 +25875,7 @@
     </row>
     <row r="17" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="8">
         <v>16331</v>
@@ -25923,7 +25916,7 @@
     </row>
     <row r="18" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="8">
         <v>2481</v>
@@ -25964,7 +25957,7 @@
     </row>
     <row r="19" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="8">
         <v>2384</v>
@@ -26005,7 +25998,7 @@
     </row>
     <row r="20" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8">
         <v>12187</v>
@@ -26046,7 +26039,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="8">
         <v>4763</v>
@@ -26087,7 +26080,7 @@
     </row>
     <row r="22" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="8">
         <v>2353</v>
@@ -26128,7 +26121,7 @@
     </row>
     <row r="23" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8">
         <v>12743</v>
@@ -26169,7 +26162,7 @@
     </row>
     <row r="24" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="8">
         <v>1250</v>
@@ -26210,7 +26203,7 @@
     </row>
     <row r="25" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="8">
         <v>6422</v>
@@ -26251,7 +26244,7 @@
     </row>
     <row r="26" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8">
         <v>11335</v>
@@ -26292,7 +26285,7 @@
     </row>
     <row r="27" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="8">
         <v>6690</v>
@@ -26333,7 +26326,7 @@
     </row>
     <row r="28" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>155897</v>
@@ -26374,7 +26367,7 @@
     </row>
     <row r="29" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="8">
         <v>44669</v>
@@ -26415,7 +26408,7 @@
     </row>
     <row r="30" spans="1:13" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>111228</v>
@@ -26486,85 +26479,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="34" t="s">
+      <c r="E1" s="33"/>
+      <c r="F1" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="34" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="45" t="s">
+      <c r="I1" s="56"/>
+      <c r="J1" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="I1" s="46"/>
-      <c r="J1" s="34" t="s">
+      <c r="K1" s="33"/>
+      <c r="L1" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="45" t="s">
+      <c r="M1" s="56"/>
+      <c r="N1" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="M1" s="46"/>
-      <c r="N1" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="O1" s="41"/>
-      <c r="P1" s="33"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="31"/>
     </row>
     <row r="2" spans="1:16" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="M2" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="N2" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="O2" s="11" t="s">
+      <c r="P2" s="11" t="s">
         <v>94</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -26669,7 +26662,7 @@
     </row>
     <row r="5" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="8">
         <v>21402</v>
@@ -26719,7 +26712,7 @@
     </row>
     <row r="6" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="8">
         <v>12000</v>
@@ -26769,7 +26762,7 @@
     </row>
     <row r="7" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>18099</v>
@@ -26819,7 +26812,7 @@
     </row>
     <row r="8" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="8">
         <v>17584</v>
@@ -26869,7 +26862,7 @@
     </row>
     <row r="9" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8">
         <v>13127</v>
@@ -26919,7 +26912,7 @@
     </row>
     <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8">
         <v>26831</v>
@@ -26969,7 +26962,7 @@
     </row>
     <row r="11" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>912</v>
@@ -27019,7 +27012,7 @@
     </row>
     <row r="12" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="8">
         <v>3114</v>
@@ -27069,7 +27062,7 @@
     </row>
     <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="8">
         <v>10831</v>
@@ -27119,7 +27112,7 @@
     </row>
     <row r="14" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="8">
         <v>2822</v>
@@ -27169,7 +27162,7 @@
     </row>
     <row r="15" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8">
         <v>6130</v>
@@ -27219,7 +27212,7 @@
     </row>
     <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="8">
         <v>1705</v>
@@ -27269,7 +27262,7 @@
     </row>
     <row r="17" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="8">
         <v>22323</v>
@@ -27319,7 +27312,7 @@
     </row>
     <row r="18" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="8">
         <v>5439</v>
@@ -27369,7 +27362,7 @@
     </row>
     <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="8">
         <v>6892</v>
@@ -27419,7 +27412,7 @@
     </row>
     <row r="20" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="8">
         <v>22044</v>
@@ -27469,7 +27462,7 @@
     </row>
     <row r="21" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="8">
         <v>11297</v>
@@ -27519,7 +27512,7 @@
     </row>
     <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="8">
         <v>6528</v>
@@ -27569,7 +27562,7 @@
     </row>
     <row r="23" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8">
         <v>25541</v>
@@ -27619,7 +27612,7 @@
     </row>
     <row r="24" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="8">
         <v>4619</v>
@@ -27669,7 +27662,7 @@
     </row>
     <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="8">
         <v>11433</v>
@@ -27719,7 +27712,7 @@
     </row>
     <row r="26" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="8">
         <v>18247</v>
@@ -27769,7 +27762,7 @@
     </row>
     <row r="27" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="8">
         <v>16981</v>
@@ -27819,7 +27812,7 @@
     </row>
     <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>327212</v>
@@ -27869,7 +27862,7 @@
     </row>
     <row r="29" spans="1:16" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="8">
         <v>59262</v>
@@ -27919,7 +27912,7 @@
     </row>
     <row r="30" spans="1:16" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>267950</v>
@@ -28009,89 +28002,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="49" t="s">
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="49" t="s">
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="61"/>
+    </row>
+    <row r="2" spans="1:19" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="58"/>
+      <c r="B2" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="51"/>
-    </row>
-    <row r="2" spans="1:19" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="F2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="M2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="N2" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="R2" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>102</v>
-      </c>
       <c r="S2" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -28214,7 +28207,7 @@
     </row>
     <row r="5" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="7">
         <v>166</v>
@@ -28273,7 +28266,7 @@
     </row>
     <row r="6" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="7">
         <v>39</v>
@@ -28332,7 +28325,7 @@
     </row>
     <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7">
         <v>89</v>
@@ -28391,7 +28384,7 @@
     </row>
     <row r="8" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="7">
         <v>135</v>
@@ -28450,7 +28443,7 @@
     </row>
     <row r="9" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="7">
         <v>153</v>
@@ -28509,7 +28502,7 @@
     </row>
     <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="7">
         <v>202</v>
@@ -28568,7 +28561,7 @@
     </row>
     <row r="11" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>1</v>
@@ -28627,7 +28620,7 @@
     </row>
     <row r="12" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7">
         <v>30</v>
@@ -28686,7 +28679,7 @@
     </row>
     <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="7">
         <v>75</v>
@@ -28745,7 +28738,7 @@
     </row>
     <row r="14" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7">
         <v>17</v>
@@ -28804,7 +28797,7 @@
     </row>
     <row r="15" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="7">
         <v>97</v>
@@ -28863,7 +28856,7 @@
     </row>
     <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7">
         <v>25</v>
@@ -28922,7 +28915,7 @@
     </row>
     <row r="17" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="7">
         <v>134</v>
@@ -28981,7 +28974,7 @@
     </row>
     <row r="18" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="7">
         <v>21</v>
@@ -29040,7 +29033,7 @@
     </row>
     <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="7">
         <v>87</v>
@@ -29099,7 +29092,7 @@
     </row>
     <row r="20" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="7">
         <v>213</v>
@@ -29158,7 +29151,7 @@
     </row>
     <row r="21" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="7">
         <v>71</v>
@@ -29217,7 +29210,7 @@
     </row>
     <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="7">
         <v>48</v>
@@ -29276,7 +29269,7 @@
     </row>
     <row r="23" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="7">
         <v>133</v>
@@ -29335,7 +29328,7 @@
     </row>
     <row r="24" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="7">
         <v>74</v>
@@ -29394,7 +29387,7 @@
     </row>
     <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="7">
         <v>78</v>
@@ -29453,7 +29446,7 @@
     </row>
     <row r="26" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="7">
         <v>183</v>
@@ -29512,7 +29505,7 @@
     </row>
     <row r="27" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="7">
         <v>83</v>
@@ -29571,7 +29564,7 @@
     </row>
     <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="10">
         <v>2417</v>
@@ -29630,7 +29623,7 @@
     </row>
     <row r="29" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="7">
         <v>435</v>
@@ -29689,7 +29682,7 @@
     </row>
     <row r="30" spans="1:19" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8">
         <v>1982</v>
